--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_385_R41.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_385_R41.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4942</v>
+        <v>7.2664</v>
       </c>
       <c r="E2" t="n">
-        <v>7.974</v>
+        <v>8.4229</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4798</v>
+        <v>-1.1566</v>
       </c>
       <c r="G2" t="n">
         <v>6.6411</v>
@@ -610,13 +610,13 @@
         <v>2.0473</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7183</v>
+        <v>0.0539</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2273</v>
+        <v>0.2216</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4909</v>
+        <v>-0.1677</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2485</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4323</v>
+        <v>5.4934</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5096</v>
+        <v>3.7969</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9227</v>
+        <v>1.6965</v>
       </c>
       <c r="G3" t="n">
         <v>6.0142</v>
@@ -688,13 +688,13 @@
         <v>2.0473</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.127</v>
+        <v>-0.0659</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0837</v>
+        <v>0.2036</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0433</v>
+        <v>-0.2696</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9306</v>
+        <v>4.7761</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7366</v>
+        <v>3.8085</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1939</v>
+        <v>0.9677</v>
       </c>
       <c r="G4" t="n">
         <v>2.3003</v>
@@ -766,13 +766,13 @@
         <v>1.5923</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8787</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5029</v>
+        <v>0.5748</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3758</v>
+        <v>0.1495</v>
       </c>
       <c r="V4" t="n">
         <v>0.3867</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4319</v>
+        <v>1.7853</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4266</v>
+        <v>1.9417</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0053</v>
+        <v>-0.1563</v>
       </c>
       <c r="G5" t="n">
         <v>1.4085</v>
@@ -844,13 +844,13 @@
         <v>2.0473</v>
       </c>
       <c r="S5" t="n">
-        <v>0.886</v>
+        <v>0.2394</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7784</v>
+        <v>0.2934</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1076</v>
+        <v>-0.054</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5451</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4685</v>
+        <v>1.1042</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6436</v>
+        <v>-1.1048</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1121</v>
+        <v>2.2091</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0962</v>
@@ -922,13 +922,13 @@
         <v>1.5923</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4143</v>
+        <v>0.2214</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1317</v>
+        <v>0.4071</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2826</v>
+        <v>-0.1857</v>
       </c>
       <c r="V6" t="n">
         <v>0.3867</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2674</v>
+        <v>0.5404</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0317</v>
+        <v>2.4986</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7642</v>
+        <v>-1.9582</v>
       </c>
       <c r="G7" t="n">
         <v>0.5291</v>
@@ -1000,13 +1000,13 @@
         <v>0.9099</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0815</v>
+        <v>0.1916</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5626</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4812</v>
+        <v>0.2872</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0901</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9574</v>
+        <v>-0.4905</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.914</v>
+        <v>-0.6087</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0434</v>
+        <v>0.1182</v>
       </c>
       <c r="G9" t="n">
         <v>0.2369</v>
@@ -1156,13 +1156,13 @@
         <v>1.1374</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4909</v>
+        <v>-0.024</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2873</v>
+        <v>0.018</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2036</v>
+        <v>-0.0419</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7034</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0094</v>
+        <v>-0.6916</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1288</v>
+        <v>0.1557</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1382</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7246</v>
@@ -1234,13 +1234,13 @@
         <v>0.4549</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7398</v>
+        <v>-0.422</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1555</v>
+        <v>-0.1286</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5843</v>
+        <v>-0.2934</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4196</v>
+        <v>-2.4131</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9006</v>
+        <v>-3.5215</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.519</v>
+        <v>1.1084</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.356</v>
+        <v>-0.6747</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8385</v>
+        <v>0.0199</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5175</v>
+        <v>-0.6945</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4845</v>
+        <v>-0.5285</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4719</v>
+        <v>0.138</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9564</v>
+        <v>-0.6665</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8715</v>
+        <v>-0.1462</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3104</v>
+        <v>-0.1182</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4389</v>
+        <v>-0.028</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2275</v>
+        <v>-2.2747</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3648</v>
+        <v>-3.4121</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5923</v>
+        <v>1.1374</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2539</v>
+        <v>0.1496</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3354</v>
+        <v>0.4191</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0815</v>
+        <v>-0.2695</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5451</v>
+        <v>0.3867</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3867</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1583</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5244</v>
+        <v>-2.8202</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6651</v>
+        <v>-2.2688</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1407</v>
+        <v>-0.5513</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6747</v>
+        <v>-2.356</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0199</v>
+        <v>-1.8385</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6945</v>
+        <v>-0.5175</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5285</v>
+        <v>-0.4845</v>
       </c>
       <c r="K12" t="n">
-        <v>0.138</v>
+        <v>0.4719</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6665</v>
+        <v>-0.9564</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1462</v>
+        <v>-1.8715</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1182</v>
+        <v>-2.3104</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.028</v>
+        <v>0.4389</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2747</v>
+        <v>0.2275</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4121</v>
+        <v>-1.3648</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1374</v>
+        <v>1.5923</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0383</v>
+        <v>-0.1466</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2755</v>
+        <v>-0.0328</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2372</v>
+        <v>-0.1138</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3867</v>
+        <v>-0.5451</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.3867</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3867</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.0456</v>
+        <v>14.4819</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8914</v>
+        <v>13.3279</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1542</v>
+        <v>1.1543</v>
       </c>
       <c r="G13" t="n">
         <v>11.9853</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3376000000000001</v>
+        <v>0.3375999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>11.6478</v>
@@ -1468,13 +1468,13 @@
         <v>14.7859</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3593000000000002</v>
+        <v>1.0773</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5996999999999999</v>
+        <v>2.0361</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9588</v>
+        <v>-0.9589</v>
       </c>
       <c r="V13" t="n">
         <v>-3.130400000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7648</v>
+        <v>4.4771</v>
       </c>
       <c r="E14" t="n">
-        <v>5.2847</v>
+        <v>5.5182</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5199</v>
+        <v>-1.0411</v>
       </c>
       <c r="G14" t="n">
         <v>3.965</v>
@@ -1546,13 +1546,13 @@
         <v>1.5923</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5387999999999999</v>
+        <v>0.1736</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1555</v>
+        <v>0.078</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3833</v>
+        <v>0.0956</v>
       </c>
       <c r="V14" t="n">
         <v>1.2485</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5597</v>
+        <v>1.1272</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4828</v>
+        <v>1.006</v>
       </c>
       <c r="F15" t="n">
-        <v>0.077</v>
+        <v>0.1212</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0278</v>
+        <v>1.4463</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0334</v>
+        <v>1.8295</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0612</v>
+        <v>-0.3832</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5847</v>
+        <v>3.3458</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5847</v>
+        <v>2.8947</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.4511</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6126</v>
+        <v>-1.8995</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5513</v>
+        <v>-1.0652</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0612</v>
+        <v>-0.8343</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2275</v>
+        <v>-2.2747</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2275</v>
+        <v>-3.4121</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4549</v>
+        <v>1.1374</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3601</v>
+        <v>0.4788</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1255</v>
+        <v>-0.0178</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2346</v>
+        <v>0.4967</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4768</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3867</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4313</v>
+        <v>0.8066</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2394</v>
+        <v>0.6623</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1918</v>
+        <v>0.1444</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4463</v>
+        <v>-0.4923</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8295</v>
+        <v>0.0052</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3832</v>
+        <v>-0.4976</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3458</v>
+        <v>0.5065</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8947</v>
+        <v>0.7591</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4511</v>
+        <v>-0.2526</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8995</v>
+        <v>-0.9988</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0652</v>
+        <v>-0.7539</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8343</v>
+        <v>-0.2449</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.2747</v>
+        <v>0.9099</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4121</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1374</v>
+        <v>0.9099</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7829</v>
+        <v>0.3891</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2156</v>
+        <v>0.1558</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5673</v>
+        <v>0.2333</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4768</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0901</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1766</v>
+        <v>0.3673</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1292</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0474</v>
+        <v>-0.1816</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4923</v>
+        <v>-0.0278</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0052</v>
+        <v>0.0334</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4976</v>
+        <v>-0.0612</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5065</v>
+        <v>0.5847</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7591</v>
+        <v>0.5847</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.2526</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9988</v>
+        <v>-0.6126</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7539</v>
+        <v>-0.5513</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2449</v>
+        <v>-0.0612</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.2275</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9099</v>
+        <v>0.4549</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7591</v>
+        <v>0.1676</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6227</v>
+        <v>0.1916</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1363</v>
+        <v>-0.024</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1913</v>
+        <v>0.3595</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5331</v>
+        <v>1.4164</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3418</v>
+        <v>-1.0568</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1012</v>
@@ -1858,13 +1858,13 @@
         <v>1.1374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1342</v>
+        <v>0.3024</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4431</v>
+        <v>0.3264</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3089</v>
+        <v>-0.024</v>
       </c>
       <c r="V18" t="n">
         <v>1.2485</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7325</v>
+        <v>-2.2498</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9874</v>
+        <v>-0.6942</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7451</v>
+        <v>-1.5556</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5233</v>
+        <v>-1.9414</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.1707</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5233</v>
+        <v>-1.7708</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7782</v>
+        <v>0.8651</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.8959</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7782</v>
+        <v>-1.0309</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7451</v>
+        <v>-2.8065</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-2.0666</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7451</v>
+        <v>-0.7399</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1374</v>
+        <v>-1.3648</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3648</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0718</v>
+        <v>-0.3083</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0718</v>
+        <v>-0.1944</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.1139</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7365</v>
+        <v>-2.7325</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2779</v>
+        <v>-1.9874</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4586</v>
+        <v>-0.7451</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9414</v>
+        <v>-1.5233</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1707</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7708</v>
+        <v>-1.5233</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8651</v>
+        <v>-0.7782</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8959</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.0309</v>
+        <v>-0.7782</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8065</v>
+        <v>-0.7451</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.0666</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7399</v>
+        <v>-0.7451</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3648</v>
+        <v>-1.1374</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3648</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.795</v>
+        <v>-0.0718</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7781</v>
+        <v>-0.0718</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0169</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8098</v>
+        <v>-2.8553</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2683</v>
+        <v>-0.5017</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5416</v>
+        <v>-2.3536</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9053</v>
@@ -2092,13 +2092,13 @@
         <v>0.4549</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1174</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6466</v>
+        <v>0.4131</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5292</v>
+        <v>-0.3412</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4768</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7217</v>
+        <v>-3.5697</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9462</v>
+        <v>-2.7319</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7755</v>
+        <v>-0.8378</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6299</v>
+        <v>-2.4889</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5172</v>
+        <v>-1.777</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1127</v>
+        <v>-0.7119</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.761</v>
+        <v>-0.6575</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0173</v>
+        <v>-0.6575</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7782</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8689</v>
+        <v>-1.8314</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5345</v>
+        <v>-1.1196</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3345</v>
+        <v>-0.7119</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9099</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1374</v>
+        <v>-2.2747</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1819</v>
+        <v>0.1257</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0478</v>
+        <v>0.042</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1341</v>
+        <v>0.0837</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1527</v>
+        <v>-3.5727</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9653</v>
+        <v>-1.8295</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1874</v>
+        <v>-1.7432</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4889</v>
+        <v>-2.6299</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.777</v>
+        <v>-0.5172</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7119</v>
+        <v>-2.1127</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6575</v>
+        <v>-0.761</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6575</v>
+        <v>0.0173</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.7782</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8314</v>
+        <v>-1.8689</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1196</v>
+        <v>-0.5345</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7119</v>
+        <v>-1.3345</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3648</v>
+        <v>-0.9099</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2747</v>
+        <v>-1.1374</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4573</v>
+        <v>-0.0329</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1915</v>
+        <v>0.0689</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2658</v>
+        <v>-0.1018</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.016</v>
+        <v>-4.4251</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2882</v>
+        <v>-1.471</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7278</v>
+        <v>-2.9541</v>
       </c>
       <c r="G24" t="n">
         <v>-4.2865</v>
@@ -2326,13 +2326,13 @@
         <v>2.0473</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7496</v>
+        <v>-0.1587</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8499</v>
+        <v>-0.0328</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1003</v>
+        <v>-0.1259</v>
       </c>
       <c r="V24" t="n">
         <v>0.475</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.0455</v>
+        <v>-12.2674</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0641000000000016</v>
+        <v>-0.0638999999999994</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.9815</v>
+        <v>-12.2033</v>
       </c>
       <c r="G25" t="n">
         <v>-11.9853</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3377000000000002</v>
+        <v>-0.3377000000000003</v>
       </c>
       <c r="I25" t="n">
         <v>-11.6478</v>
       </c>
       <c r="J25" t="n">
-        <v>6.500399999999999</v>
+        <v>6.500400000000001</v>
       </c>
       <c r="K25" t="n">
         <v>10.4173</v>
@@ -2404,13 +2404,13 @@
         <v>10.2363</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3593000000000002</v>
+        <v>1.1374</v>
       </c>
       <c r="T25" t="n">
-        <v>0.9588999999999998</v>
+        <v>0.959</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5996999999999999</v>
+        <v>0.1785</v>
       </c>
       <c r="V25" t="n">
         <v>3.1303</v>
